--- a/ONCHO/Impact Assessments/Nigeria/2025/river statesoem/ng_oncho_stop_2507_1_site_oem.xlsx
+++ b/ONCHO/Impact Assessments/Nigeria/2025/river statesoem/ng_oncho_stop_2507_1_site_oem.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Impact Assessments\Nigeria\2025\river statesoem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2E6F58-796B-4831-B0E4-B3F808719523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FAAE7F9-CB25-40F7-8970-A5338FE7B430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="233">
   <si>
     <t>type</t>
   </si>
@@ -398,12 +398,6 @@
     <t>RIVERS</t>
   </si>
   <si>
-    <t>ng_oncho_stop_2507_1_site_oem</t>
-  </si>
-  <si>
-    <t>(River - OEM - 2025 July) - 1. Site Form</t>
-  </si>
-  <si>
     <t>ABUA/ODUAL</t>
   </si>
   <si>
@@ -419,9 +413,6 @@
     <t>GOKANA</t>
   </si>
   <si>
-    <t>KHANA</t>
-  </si>
-  <si>
     <t>OBIO/AKPOR</t>
   </si>
   <si>
@@ -512,21 +503,6 @@
     <t>YEGHE</t>
   </si>
   <si>
-    <t>EEKEN</t>
-  </si>
-  <si>
-    <t>ILOLO</t>
-  </si>
-  <si>
-    <t>KONO/KWAWA</t>
-  </si>
-  <si>
-    <t>LUUBAARA</t>
-  </si>
-  <si>
-    <t>NUMAA-KAA</t>
-  </si>
-  <si>
     <t>CHOBA</t>
   </si>
   <si>
@@ -677,21 +653,6 @@
     <t>RIV_GOK_M_080</t>
   </si>
   <si>
-    <t>RIV_KHA_M_081</t>
-  </si>
-  <si>
-    <t>RIV_KHA_M_082</t>
-  </si>
-  <si>
-    <t>RIV_KHA_M_083</t>
-  </si>
-  <si>
-    <t>RIV_KHA_M_084</t>
-  </si>
-  <si>
-    <t>RIV_KHA_M_085</t>
-  </si>
-  <si>
     <t>RIV_OBA_M_086</t>
   </si>
   <si>
@@ -765,6 +726,12 @@
   </si>
   <si>
     <t>RIV_TAI_M_110</t>
+  </si>
+  <si>
+    <t>ng_oncho_stop_2507_1_site_oem_v2</t>
+  </si>
+  <si>
+    <t>(River - OEM - 2025 July) - 1. Site Form V2</t>
   </si>
 </sst>
 </file>
@@ -1695,7 +1662,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F147"/>
+  <dimension ref="A1:F136"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1998,10 +1965,10 @@
         <v>85</v>
       </c>
       <c r="B25" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C25" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>120</v>
@@ -2012,10 +1979,10 @@
         <v>85</v>
       </c>
       <c r="B26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>120</v>
@@ -2026,10 +1993,10 @@
         <v>85</v>
       </c>
       <c r="B27" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C27" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>120</v>
@@ -2040,10 +2007,10 @@
         <v>85</v>
       </c>
       <c r="B28" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C28" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>120</v>
@@ -2054,10 +2021,10 @@
         <v>85</v>
       </c>
       <c r="B29" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>120</v>
@@ -2068,10 +2035,10 @@
         <v>85</v>
       </c>
       <c r="B30" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C30" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>120</v>
@@ -2082,10 +2049,10 @@
         <v>85</v>
       </c>
       <c r="B31" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C31" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>120</v>
@@ -2096,10 +2063,10 @@
         <v>85</v>
       </c>
       <c r="B32" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C32" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>120</v>
@@ -2110,10 +2077,10 @@
         <v>85</v>
       </c>
       <c r="B33" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C33" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>120</v>
@@ -2124,44 +2091,44 @@
         <v>85</v>
       </c>
       <c r="B34" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C34" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" t="s">
-        <v>85</v>
-      </c>
-      <c r="B35" t="s">
-        <v>133</v>
-      </c>
-      <c r="C35" t="s">
-        <v>133</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>120</v>
-      </c>
+      <c r="D35" s="9"/>
     </row>
     <row r="36" spans="1:5">
-      <c r="D36" s="9"/>
+      <c r="A36" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" t="s">
+        <v>131</v>
+      </c>
+      <c r="C36" t="s">
+        <v>131</v>
+      </c>
+      <c r="E36" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
         <v>86</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C37" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2169,13 +2136,13 @@
         <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C38" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E38" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2183,13 +2150,13 @@
         <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C39" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2197,13 +2164,13 @@
         <v>86</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C40" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E40" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2211,13 +2178,13 @@
         <v>86</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C41" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E41" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2225,13 +2192,13 @@
         <v>86</v>
       </c>
       <c r="B42" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C42" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E42" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2239,13 +2206,13 @@
         <v>86</v>
       </c>
       <c r="B43" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C43" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E43" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2253,13 +2220,13 @@
         <v>86</v>
       </c>
       <c r="B44" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C44" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E44" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2267,13 +2234,13 @@
         <v>86</v>
       </c>
       <c r="B45" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C45" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E45" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2281,13 +2248,13 @@
         <v>86</v>
       </c>
       <c r="B46" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C46" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E46" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2295,13 +2262,13 @@
         <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C47" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E47" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2309,13 +2276,13 @@
         <v>86</v>
       </c>
       <c r="B48" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C48" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E48" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2323,13 +2290,13 @@
         <v>86</v>
       </c>
       <c r="B49" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C49" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E49" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2337,13 +2304,13 @@
         <v>86</v>
       </c>
       <c r="B50" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C50" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E50" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2351,13 +2318,13 @@
         <v>86</v>
       </c>
       <c r="B51" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C51" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2365,13 +2332,13 @@
         <v>86</v>
       </c>
       <c r="B52" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C52" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E52" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2379,13 +2346,13 @@
         <v>86</v>
       </c>
       <c r="B53" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C53" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E53" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2393,13 +2360,13 @@
         <v>86</v>
       </c>
       <c r="B54" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C54" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E54" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2407,13 +2374,13 @@
         <v>86</v>
       </c>
       <c r="B55" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C55" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E55" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2421,13 +2388,13 @@
         <v>86</v>
       </c>
       <c r="B56" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C56" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E56" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2435,13 +2402,13 @@
         <v>86</v>
       </c>
       <c r="B57" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C57" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E57" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2449,13 +2416,13 @@
         <v>86</v>
       </c>
       <c r="B58" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C58" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E58" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2463,13 +2430,13 @@
         <v>86</v>
       </c>
       <c r="B59" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C59" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E59" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2477,13 +2444,13 @@
         <v>86</v>
       </c>
       <c r="B60" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C60" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E60" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2491,13 +2458,13 @@
         <v>86</v>
       </c>
       <c r="B61" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C61" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2505,13 +2472,13 @@
         <v>86</v>
       </c>
       <c r="B62" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C62" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E62" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2519,13 +2486,13 @@
         <v>86</v>
       </c>
       <c r="B63" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C63" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E63" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2533,13 +2500,13 @@
         <v>86</v>
       </c>
       <c r="B64" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C64" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E64" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2547,13 +2514,13 @@
         <v>86</v>
       </c>
       <c r="B65" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C65" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E65" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2561,13 +2528,13 @@
         <v>86</v>
       </c>
       <c r="B66" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C66" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E66" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2575,13 +2542,13 @@
         <v>86</v>
       </c>
       <c r="B67" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C67" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E67" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2589,13 +2556,13 @@
         <v>86</v>
       </c>
       <c r="B68" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C68" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E68" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2603,13 +2570,13 @@
         <v>86</v>
       </c>
       <c r="B69" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C69" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E69" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2617,13 +2584,13 @@
         <v>86</v>
       </c>
       <c r="B70" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C70" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E70" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2631,13 +2598,13 @@
         <v>86</v>
       </c>
       <c r="B71" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C71" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E71" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2645,13 +2612,13 @@
         <v>86</v>
       </c>
       <c r="B72" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C72" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E72" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2659,13 +2626,13 @@
         <v>86</v>
       </c>
       <c r="B73" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C73" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E73" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2673,13 +2640,13 @@
         <v>86</v>
       </c>
       <c r="B74" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C74" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E74" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2687,13 +2654,13 @@
         <v>86</v>
       </c>
       <c r="B75" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C75" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E75" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2701,13 +2668,13 @@
         <v>86</v>
       </c>
       <c r="B76" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C76" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E76" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2715,13 +2682,13 @@
         <v>86</v>
       </c>
       <c r="B77" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C77" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E77" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2729,13 +2696,13 @@
         <v>86</v>
       </c>
       <c r="B78" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C78" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E78" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2743,13 +2710,13 @@
         <v>86</v>
       </c>
       <c r="B79" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C79" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2757,13 +2724,13 @@
         <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C80" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E80" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -2771,13 +2738,13 @@
         <v>86</v>
       </c>
       <c r="B81" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C81" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E81" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -2785,13 +2752,13 @@
         <v>86</v>
       </c>
       <c r="B82" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C82" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E82" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -2799,13 +2766,13 @@
         <v>86</v>
       </c>
       <c r="B83" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C83" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E83" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -2813,13 +2780,13 @@
         <v>86</v>
       </c>
       <c r="B84" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C84" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E84" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -2827,97 +2794,97 @@
         <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C85" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E85" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86" t="s">
-        <v>86</v>
-      </c>
-      <c r="B86" t="s">
-        <v>183</v>
-      </c>
-      <c r="C86" t="s">
-        <v>183</v>
-      </c>
-      <c r="E86" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="B87" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C87" t="s">
-        <v>184</v>
-      </c>
-      <c r="E87" t="s">
-        <v>133</v>
+        <v>181</v>
+      </c>
+      <c r="F87" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="B88" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C88" t="s">
-        <v>185</v>
-      </c>
-      <c r="E88" t="s">
-        <v>133</v>
+        <v>182</v>
+      </c>
+      <c r="F88" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="B89" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C89" t="s">
-        <v>186</v>
-      </c>
-      <c r="E89" t="s">
-        <v>133</v>
+        <v>183</v>
+      </c>
+      <c r="F89" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="B90" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C90" t="s">
-        <v>187</v>
-      </c>
-      <c r="E90" t="s">
-        <v>133</v>
+        <v>184</v>
+      </c>
+      <c r="F90" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="B91" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C91" t="s">
-        <v>188</v>
-      </c>
-      <c r="E91" t="s">
+        <v>185</v>
+      </c>
+      <c r="F91" t="s">
         <v>133</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" t="s">
+        <v>108</v>
+      </c>
+      <c r="B92" t="s">
+        <v>186</v>
+      </c>
+      <c r="C92" t="s">
+        <v>186</v>
+      </c>
+      <c r="F92" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -2925,13 +2892,13 @@
         <v>108</v>
       </c>
       <c r="B93" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C93" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F93" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -2939,13 +2906,13 @@
         <v>108</v>
       </c>
       <c r="B94" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C94" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F94" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -2953,10 +2920,10 @@
         <v>108</v>
       </c>
       <c r="B95" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C95" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F95" t="s">
         <v>137</v>
@@ -2967,13 +2934,13 @@
         <v>108</v>
       </c>
       <c r="B96" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C96" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F96" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -2981,13 +2948,13 @@
         <v>108</v>
       </c>
       <c r="B97" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C97" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F97" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -2995,10 +2962,10 @@
         <v>108</v>
       </c>
       <c r="B98" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C98" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F98" t="s">
         <v>141</v>
@@ -3009,13 +2976,13 @@
         <v>108</v>
       </c>
       <c r="B99" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C99" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F99" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -3023,13 +2990,13 @@
         <v>108</v>
       </c>
       <c r="B100" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C100" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F100" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -3037,13 +3004,13 @@
         <v>108</v>
       </c>
       <c r="B101" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C101" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F101" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -3051,13 +3018,13 @@
         <v>108</v>
       </c>
       <c r="B102" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C102" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F102" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -3065,13 +3032,13 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C103" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F103" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -3079,13 +3046,13 @@
         <v>108</v>
       </c>
       <c r="B104" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C104" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F104" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3093,13 +3060,13 @@
         <v>108</v>
       </c>
       <c r="B105" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C105" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F105" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -3107,13 +3074,13 @@
         <v>108</v>
       </c>
       <c r="B106" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C106" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F106" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -3121,13 +3088,13 @@
         <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C107" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F107" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -3135,10 +3102,10 @@
         <v>108</v>
       </c>
       <c r="B108" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C108" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F108" t="s">
         <v>152</v>
@@ -3149,13 +3116,13 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C109" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F109" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -3163,13 +3130,13 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C110" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F110" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -3177,13 +3144,13 @@
         <v>108</v>
       </c>
       <c r="B111" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C111" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F111" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -3191,13 +3158,13 @@
         <v>108</v>
       </c>
       <c r="B112" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C112" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F112" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -3205,13 +3172,13 @@
         <v>108</v>
       </c>
       <c r="B113" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C113" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F113" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -3219,13 +3186,13 @@
         <v>108</v>
       </c>
       <c r="B114" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C114" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F114" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -3233,10 +3200,10 @@
         <v>108</v>
       </c>
       <c r="B115" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C115" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F115" t="s">
         <v>156</v>
@@ -3247,13 +3214,13 @@
         <v>108</v>
       </c>
       <c r="B116" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C116" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F116" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -3261,13 +3228,13 @@
         <v>108</v>
       </c>
       <c r="B117" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C117" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F117" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -3275,13 +3242,13 @@
         <v>108</v>
       </c>
       <c r="B118" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C118" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F118" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -3289,10 +3256,10 @@
         <v>108</v>
       </c>
       <c r="B119" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C119" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F119" t="s">
         <v>163</v>
@@ -3303,13 +3270,13 @@
         <v>108</v>
       </c>
       <c r="B120" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C120" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F120" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -3317,13 +3284,13 @@
         <v>108</v>
       </c>
       <c r="B121" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C121" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F121" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -3331,13 +3298,13 @@
         <v>108</v>
       </c>
       <c r="B122" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C122" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F122" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -3345,13 +3312,13 @@
         <v>108</v>
       </c>
       <c r="B123" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C123" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F123" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -3359,13 +3326,13 @@
         <v>108</v>
       </c>
       <c r="B124" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C124" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F124" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -3373,13 +3340,13 @@
         <v>108</v>
       </c>
       <c r="B125" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C125" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F125" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -3387,13 +3354,13 @@
         <v>108</v>
       </c>
       <c r="B126" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C126" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F126" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -3401,13 +3368,13 @@
         <v>108</v>
       </c>
       <c r="B127" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C127" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F127" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -3415,13 +3382,13 @@
         <v>108</v>
       </c>
       <c r="B128" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C128" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F128" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -3429,13 +3396,13 @@
         <v>108</v>
       </c>
       <c r="B129" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C129" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F129" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -3443,13 +3410,13 @@
         <v>108</v>
       </c>
       <c r="B130" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C130" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F130" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -3457,13 +3424,13 @@
         <v>108</v>
       </c>
       <c r="B131" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C131" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F131" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -3471,13 +3438,13 @@
         <v>108</v>
       </c>
       <c r="B132" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C132" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F132" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -3485,13 +3452,13 @@
         <v>108</v>
       </c>
       <c r="B133" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C133" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F133" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -3499,13 +3466,13 @@
         <v>108</v>
       </c>
       <c r="B134" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C134" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F134" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -3513,13 +3480,13 @@
         <v>108</v>
       </c>
       <c r="B135" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C135" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F135" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -3527,173 +3494,19 @@
         <v>108</v>
       </c>
       <c r="B136" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C136" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F136" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
-      <c r="A137" t="s">
-        <v>108</v>
-      </c>
-      <c r="B137" t="s">
-        <v>233</v>
-      </c>
-      <c r="C137" t="s">
-        <v>233</v>
-      </c>
-      <c r="F137" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
-      <c r="A138" t="s">
-        <v>108</v>
-      </c>
-      <c r="B138" t="s">
-        <v>234</v>
-      </c>
-      <c r="C138" t="s">
-        <v>234</v>
-      </c>
-      <c r="F138" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
-      <c r="A139" t="s">
-        <v>108</v>
-      </c>
-      <c r="B139" t="s">
-        <v>235</v>
-      </c>
-      <c r="C139" t="s">
-        <v>235</v>
-      </c>
-      <c r="F139" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6">
-      <c r="A140" t="s">
-        <v>108</v>
-      </c>
-      <c r="B140" t="s">
-        <v>236</v>
-      </c>
-      <c r="C140" t="s">
-        <v>236</v>
-      </c>
-      <c r="F140" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
-      <c r="A141" t="s">
-        <v>108</v>
-      </c>
-      <c r="B141" t="s">
-        <v>237</v>
-      </c>
-      <c r="C141" t="s">
-        <v>237</v>
-      </c>
-      <c r="F141" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
-      <c r="A142" t="s">
-        <v>108</v>
-      </c>
-      <c r="B142" t="s">
-        <v>238</v>
-      </c>
-      <c r="C142" t="s">
-        <v>238</v>
-      </c>
-      <c r="F142" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
-      <c r="A143" t="s">
-        <v>108</v>
-      </c>
-      <c r="B143" t="s">
-        <v>239</v>
-      </c>
-      <c r="C143" t="s">
-        <v>239</v>
-      </c>
-      <c r="F143" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6">
-      <c r="A144" t="s">
-        <v>108</v>
-      </c>
-      <c r="B144" t="s">
-        <v>240</v>
-      </c>
-      <c r="C144" t="s">
-        <v>240</v>
-      </c>
-      <c r="F144" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
-      <c r="A145" t="s">
-        <v>108</v>
-      </c>
-      <c r="B145" t="s">
-        <v>241</v>
-      </c>
-      <c r="C145" t="s">
-        <v>241</v>
-      </c>
-      <c r="F145" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="A146" t="s">
-        <v>108</v>
-      </c>
-      <c r="B146" t="s">
-        <v>242</v>
-      </c>
-      <c r="C146" t="s">
-        <v>242</v>
-      </c>
-      <c r="F146" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
-      <c r="A147" t="s">
-        <v>108</v>
-      </c>
-      <c r="B147" t="s">
-        <v>243</v>
-      </c>
-      <c r="C147" t="s">
-        <v>243</v>
-      </c>
-      <c r="F147" t="s">
-        <v>188</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A41:E48">
-    <sortCondition ref="A41:A48"/>
-    <sortCondition ref="E41:E48"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A40:E47">
+    <sortCondition ref="A40:A47"/>
+    <sortCondition ref="E40:E47"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3722,10 +3535,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13" t="s">
-        <v>122</v>
+        <v>232</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>121</v>
+        <v>231</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>112</v>
